--- a/storage/templates/modelo_padrao_difal.xlsx
+++ b/storage/templates/modelo_padrao_difal.xlsx
@@ -235,6 +235,366 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1543050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1805,6 +2165,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3093,6 +3454,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4381,6 +4743,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5669,6 +6032,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6957,6 +7321,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8245,6 +8610,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9533,6 +9899,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10821,6 +11188,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12109,6 +12477,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13397,6 +13766,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14685,6 +15055,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15973,5 +16344,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>